--- a/Phenotype/Tables/EPS_TableS7C_FromR.xlsx
+++ b/Phenotype/Tables/EPS_TableS7C_FromR.xlsx
@@ -438,7 +438,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.001</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.100</t>
+          <t>0.101</t>
         </is>
       </c>
     </row>
@@ -570,7 +570,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.344</t>
+          <t>0.343</t>
         </is>
       </c>
     </row>
